--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487092_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487092_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.6326</v>
+        <v>6.5303</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4115</v>
+        <v>5.2461</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2212</v>
+        <v>1.2842</v>
       </c>
       <c r="G2" t="n">
         <v>2.0995</v>
@@ -610,13 +610,13 @@
         <v>2.8951</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5284</v>
+        <v>1.4261</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3645</v>
+        <v>1.1991</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1639</v>
+        <v>0.227</v>
       </c>
       <c r="V2" t="n">
         <v>3.9698</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MARCOS SÁNCHEZ</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2204</v>
+        <v>1.1028</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5978</v>
+        <v>0.6186</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3774</v>
+        <v>0.4842</v>
       </c>
       <c r="G3" t="n">
-        <v>3.101</v>
+        <v>1.5777</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0775</v>
+        <v>0.3603</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0235</v>
+        <v>1.2174</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9792</v>
+        <v>2.618</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0828</v>
+        <v>0.828</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8964</v>
+        <v>1.7901</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1218</v>
+        <v>-1.0403</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9947</v>
+        <v>-0.4677</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1271</v>
+        <v>-0.5727</v>
       </c>
       <c r="P3" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.158</v>
+        <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3318</v>
+        <v>-0.6752</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4164</v>
+        <v>-0.0694</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.6058</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.7418</v>
+        <v>-0.5717</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7418</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LOPEZ RAMOS</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0135</v>
+        <v>0.8642</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2762</v>
+        <v>-0.6342</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2897</v>
+        <v>1.4984</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9937</v>
+        <v>-0.8137</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.5402</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.2735</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2129</v>
+        <v>0.1666</v>
       </c>
       <c r="K4" t="n">
-        <v>0.414</v>
+        <v>0.1344</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6269</v>
+        <v>0.0321</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7808</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5009</v>
+        <v>-0.6747</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2799</v>
+        <v>-0.3056</v>
       </c>
       <c r="P4" t="n">
-        <v>0.386</v>
+        <v>1.9301</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>0.386</v>
+        <v>2.8951</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5942</v>
+        <v>-0.2522</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4891</v>
+        <v>-0.1216</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1051</v>
+        <v>-0.1306</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>A. MARCOS SÁNCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1282</v>
+        <v>0.7271</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3322</v>
+        <v>1.158</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2039</v>
+        <v>-0.4309</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8137</v>
+        <v>3.101</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5402</v>
+        <v>1.0775</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2735</v>
+        <v>2.0235</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1666</v>
+        <v>1.9792</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1344</v>
+        <v>0.0828</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0321</v>
+        <v>1.8964</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9802999999999999</v>
+        <v>1.1218</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6747</v>
+        <v>0.9947</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3056</v>
+        <v>0.1271</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8951</v>
+        <v>1.158</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2446</v>
+        <v>0.1748</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8196</v>
+        <v>0.1438</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.425</v>
+        <v>0.031</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.7418</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2859</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4463</v>
+        <v>0.5531</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5494</v>
+        <v>0.2894</v>
       </c>
       <c r="F6" t="n">
-        <v>0.103</v>
+        <v>0.2636</v>
       </c>
       <c r="G6" t="n">
         <v>-3.9153</v>
@@ -922,13 +922,13 @@
         <v>2.1231</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0219</v>
+        <v>-0.0225</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5816</v>
+        <v>0.2572</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4402</v>
+        <v>-0.2796</v>
       </c>
       <c r="V6" t="n">
         <v>4.2979</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>S. LOPEZ RAMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4846</v>
+        <v>-0.2474</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6208</v>
+        <v>0.1761</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1362</v>
+        <v>-0.4235</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5777</v>
+        <v>-0.9937</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3603</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2174</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>2.618</v>
+        <v>-0.2129</v>
       </c>
       <c r="K7" t="n">
-        <v>0.828</v>
+        <v>0.414</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7901</v>
+        <v>-0.6269</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0403</v>
+        <v>-0.7808</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4677</v>
+        <v>-0.5009</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5727</v>
+        <v>-0.2799</v>
       </c>
       <c r="P7" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7021</v>
+        <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.2626</v>
+        <v>0.3602</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3087</v>
+        <v>0.389</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9538</v>
+        <v>-0.0288</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5653</v>
+        <v>-1.606</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.987</v>
+        <v>-2.0276</v>
       </c>
       <c r="F8" t="n">
         <v>0.4217</v>
@@ -1078,10 +1078,10 @@
         <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2816</v>
+        <v>0.2409</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2512</v>
+        <v>0.2105</v>
       </c>
       <c r="U8" t="n">
         <v>0.0304</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0093</v>
+        <v>-2.3038</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1773</v>
+        <v>-3.4182</v>
       </c>
       <c r="F9" t="n">
-        <v>1.168</v>
+        <v>1.1144</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2611</v>
@@ -1156,13 +1156,13 @@
         <v>1.5441</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6028</v>
+        <v>0.3083</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8593</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2565</v>
+        <v>-0.31</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.958</v>
+        <v>-2.3919</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6161</v>
+        <v>-0.2374</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3419</v>
+        <v>-2.1545</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6143</v>
@@ -1234,13 +1234,13 @@
         <v>1.7371</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.509</v>
+        <v>-0.9429</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1303</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3788</v>
+        <v>-0.1914</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5717</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2361</v>
+        <v>-2.7294</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2543</v>
+        <v>-1.9351</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9817</v>
+        <v>-0.7943</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4087</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5294</v>
+        <v>-0.0228</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0132</v>
+        <v>0.3325</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5427</v>
+        <v>-0.3553</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9883000000000011</v>
+        <v>0.499000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.251600000000001</v>
+        <v>-0.7643000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2633</v>
+        <v>1.263299999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-8.0755</v>
@@ -1360,7 +1360,7 @@
         <v>0.6676</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.7432</v>
+        <v>-8.743200000000002</v>
       </c>
       <c r="J12" t="n">
         <v>-0.6725999999999994</v>
@@ -1390,13 +1390,13 @@
         <v>18.3357</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8922999999999998</v>
+        <v>0.5947</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7207000000000005</v>
+        <v>2.208</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.613</v>
+        <v>-1.6131</v>
       </c>
       <c r="V12" t="n">
         <v>3.154500000000001</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0839</v>
+        <v>5.4831</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9318</v>
+        <v>5.3309</v>
       </c>
       <c r="F13" t="n">
         <v>0.1521</v>
@@ -1468,10 +1468,10 @@
         <v>2.7021</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0536</v>
+        <v>0.4528</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3326</v>
+        <v>0.7318</v>
       </c>
       <c r="U13" t="n">
         <v>-0.279</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8542</v>
+        <v>1.8205</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0186</v>
+        <v>-0.9185</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8728</v>
+        <v>2.7389</v>
       </c>
       <c r="G14" t="n">
         <v>1.5612</v>
@@ -1546,13 +1546,13 @@
         <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4158</v>
+        <v>0.3821</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2551</v>
+        <v>-0.155</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.537</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1228</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4925</v>
+        <v>1.1852</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2226</v>
+        <v>-0.4229</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7152</v>
+        <v>1.6081</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9811</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8196</v>
+        <v>0.5123</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3385</v>
+        <v>0.1382</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4812</v>
+        <v>0.3741</v>
       </c>
       <c r="V15" t="n">
         <v>2.619</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8211000000000001</v>
+        <v>1.0482</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6131</v>
+        <v>0.8134</v>
       </c>
       <c r="F16" t="n">
-        <v>0.208</v>
+        <v>0.2347</v>
       </c>
       <c r="G16" t="n">
         <v>0.4173</v>
@@ -1702,13 +1702,13 @@
         <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5612</v>
+        <v>-0.3341</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1044</v>
+        <v>0.0959</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4567</v>
+        <v>-0.43</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. ECHEONDO LACALLE</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6494</v>
+        <v>-0.1406</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2315</v>
+        <v>0.714</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4179</v>
+        <v>-0.8546</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0618</v>
+        <v>1.05</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1303</v>
+        <v>1.3414</v>
       </c>
       <c r="I17" t="n">
-        <v>0.06850000000000001</v>
+        <v>-0.2913</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1849</v>
+        <v>0.4221</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1035</v>
+        <v>0.9676</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0814</v>
+        <v>-0.5455</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2467</v>
+        <v>0.6279</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2338</v>
+        <v>0.3737</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0129</v>
+        <v>0.2542</v>
       </c>
       <c r="P17" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9736</v>
+        <v>-0.6418</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4164</v>
+        <v>0.2918</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5572</v>
+        <v>-0.9337</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>I. ECHEONDO LACALLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8822</v>
+        <v>-0.1616</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2133</v>
+        <v>0.0689</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0955</v>
+        <v>-0.2305</v>
       </c>
       <c r="G18" t="n">
-        <v>1.05</v>
+        <v>-0.0618</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3414</v>
+        <v>-0.1303</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2913</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4221</v>
+        <v>0.1849</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9676</v>
+        <v>0.1035</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5455</v>
+        <v>0.0814</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6279</v>
+        <v>-0.2467</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3737</v>
+        <v>-0.2338</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2542</v>
+        <v>-0.0129</v>
       </c>
       <c r="P18" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3834</v>
+        <v>-0.4858</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2089</v>
+        <v>-0.116</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1746</v>
+        <v>-0.3698</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.061</v>
+        <v>-0.8135</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3385</v>
+        <v>-2.2364</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7225</v>
+        <v>1.4229</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1385</v>
+        <v>-1.3289</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1178</v>
+        <v>0.3612</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0207</v>
+        <v>-1.6901</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7643</v>
+        <v>-0.9288</v>
       </c>
       <c r="K19" t="n">
-        <v>0.926</v>
+        <v>0.3414</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8383</v>
+        <v>-1.2702</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3742</v>
+        <v>-0.4001</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8082</v>
+        <v>0.0198</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1824</v>
+        <v>-0.4199</v>
       </c>
       <c r="P19" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-2.8951</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.9301</v>
+        <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3709</v>
+        <v>0.1593</v>
       </c>
       <c r="T19" t="n">
-        <v>0.591</v>
+        <v>-0.2581</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7799</v>
+        <v>0.4174</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.6053</v>
+        <v>0.1631</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2014</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.8067</v>
+        <v>0.2476</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1175</v>
+        <v>-0.8567</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2503</v>
+        <v>-1.1502</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1328</v>
+        <v>0.2935</v>
       </c>
       <c r="G20" t="n">
         <v>0.909</v>
@@ -2014,13 +2014,13 @@
         <v>0.579</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4125</v>
+        <v>-0.1517</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0278</v>
+        <v>0.1279</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4402</v>
+        <v>-0.2796</v>
       </c>
       <c r="V20" t="n">
         <v>-1.228</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4399</v>
+        <v>-1.3328</v>
       </c>
       <c r="E21" t="n">
         <v>-1.5525</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1126</v>
+        <v>0.2197</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9874000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1666</v>
+        <v>-0.0595</v>
       </c>
       <c r="T21" t="n">
         <v>-0.238</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1785</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2859</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5551</v>
+        <v>-2.0039</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7371</v>
+        <v>-0.6389</v>
       </c>
       <c r="F22" t="n">
-        <v>1.182</v>
+        <v>-1.365</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3289</v>
+        <v>2.1385</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3612</v>
+        <v>0.1178</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6901</v>
+        <v>2.0207</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9288</v>
+        <v>1.7643</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3414</v>
+        <v>0.926</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2702</v>
+        <v>0.8383</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4001</v>
+        <v>0.3742</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0198</v>
+        <v>-0.8082</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4199</v>
+        <v>1.1824</v>
       </c>
       <c r="P22" t="n">
-        <v>0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R22" t="n">
-        <v>1.158</v>
+        <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5823</v>
+        <v>0.428</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7588</v>
+        <v>0.2905</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1765</v>
+        <v>0.1374</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1631</v>
+        <v>-3.6053</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.2014</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2476</v>
+        <v>-3.8067</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5584</v>
+        <v>-3.2396</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6703</v>
+        <v>-1.2712</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8881</v>
+        <v>-1.9684</v>
       </c>
       <c r="G23" t="n">
         <v>2.0523</v>
@@ -2248,13 +2248,13 @@
         <v>0.965</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3121</v>
+        <v>0.6309</v>
       </c>
       <c r="T23" t="n">
-        <v>1.3048</v>
+        <v>0.704</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0073</v>
+        <v>-0.0731</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0277</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9882000000000004</v>
+        <v>0.9883000000000011</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2632</v>
+        <v>-1.2634</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2515</v>
+        <v>2.251400000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>8.075500000000002</v>
+        <v>8.075499999999998</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6676000000000002</v>
+        <v>-0.6676000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>8.7433</v>
@@ -2308,13 +2308,13 @@
         <v>4.263</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6725</v>
+        <v>0.6725000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>-3.8078</v>
       </c>
       <c r="O24" t="n">
-        <v>4.480399999999999</v>
+        <v>4.4804</v>
       </c>
       <c r="P24" t="n">
         <v>-4.8252</v>
@@ -2326,13 +2326,13 @@
         <v>13.5104</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8924</v>
+        <v>0.8924999999999998</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6131</v>
+        <v>1.613</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7205</v>
+        <v>-0.7208000000000003</v>
       </c>
       <c r="V24" t="n">
         <v>-3.154399999999999</v>
